--- a/docs/03_test/従業員更新のテストケース.xlsx
+++ b/docs/03_test/従業員更新のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBED6A5-DFC0-42F1-9850-344CD91597C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4D36B7-2C45-4BDD-9F0D-1ED2FB245910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D9AB3BAF-20C1-4D8C-BC05-5EA19822F61D}"/>
   </bookViews>
@@ -839,17 +839,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -858,31 +849,40 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -996,50 +996,6 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2463851</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1177637</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B75583-8C08-F168-B16C-36FFBF3F0214}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6511636" y="6534727"/>
-          <a:ext cx="2463851" cy="1177637"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
@@ -1063,7 +1019,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1107,7 +1063,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1151,7 +1107,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1195,7 +1151,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1239,7 +1195,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1283,7 +1239,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1327,7 +1283,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1371,7 +1327,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1415,7 +1371,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1459,7 +1415,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1503,7 +1459,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1547,7 +1503,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1591,7 +1547,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1635,7 +1591,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1679,7 +1635,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1723,7 +1679,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1767,7 +1723,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1788,21 +1744,65 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2447637</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>944464</xdr:rowOff>
+      <xdr:colOff>2525059</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1185056</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="図 39">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25512605-2976-353B-A248-B170ACF03166}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8827CF20-9A89-6414-055B-EE6F87026FBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9943353" y="7239000"/>
+          <a:ext cx="2525059" cy="1185056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2159000</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>133119</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6967BE5F-3DCA-E7B8-1232-C88DFA51F3E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1818,8 +1818,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="36252727"/>
-          <a:ext cx="2447637" cy="1371646"/>
+          <a:off x="9985375" y="35163126"/>
+          <a:ext cx="2159000" cy="1688868"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2134,133 +2134,133 @@
     <col min="3" max="3" width="24.9140625" customWidth="1"/>
     <col min="4" max="4" width="15.9140625" customWidth="1"/>
     <col min="6" max="6" width="30.1640625" customWidth="1"/>
-    <col min="7" max="7" width="33.6640625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="33.6640625" style="4" customWidth="1"/>
     <col min="8" max="8" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="41.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="12"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" spans="1:8" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5" t="s">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="140" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7" t="s">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="8"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="149.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="8" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2268,14 +2268,14 @@
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="8" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2283,14 +2283,14 @@
       <c r="A18">
         <v>4</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="8" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2298,566 +2298,566 @@
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="8" t="s">
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
     </row>
     <row r="21" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>1</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="7" t="s">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="10">
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="15">
         <v>2</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="4"/>
+      <c r="G22" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="10"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="15"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="8"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
     </row>
     <row r="25" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>1</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="7" t="s">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H25" s="8"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="10">
+      <c r="A26" s="15">
         <v>2</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="4" t="s">
+      <c r="F26" s="3"/>
+      <c r="G26" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="8"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="90" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="10"/>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="15"/>
+      <c r="B27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="8"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>1</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7" t="s">
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H29" s="8"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="10">
+      <c r="A30" s="15">
         <v>2</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="4" t="s">
+      <c r="F30" s="3"/>
+      <c r="G30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="8"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="108" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="10"/>
-      <c r="B31" s="8" t="s">
+      <c r="A31" s="15"/>
+      <c r="B31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="8"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
     </row>
     <row r="33" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>1</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7" t="s">
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H33" s="8"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="10">
+      <c r="A34" s="15">
         <v>2</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="10"/>
-      <c r="B35" s="8" t="s">
+      <c r="A35" s="15"/>
+      <c r="B35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="8"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
     </row>
     <row r="37" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>1</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="7" t="s">
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H37" s="8"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="10">
+      <c r="A38" s="15">
         <v>2</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="7"/>
-      <c r="H38" s="8"/>
+      <c r="F38" s="3"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="10"/>
-      <c r="B39" s="8" t="s">
+      <c r="A39" s="15"/>
+      <c r="B39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H39" s="8"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
     </row>
     <row r="41" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>1</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="7" t="s">
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H41" s="8"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="51.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="10">
+      <c r="A42" s="15">
         <v>2</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="7"/>
-      <c r="H42" s="8"/>
+      <c r="F42" s="3"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="116.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="10"/>
-      <c r="B43" s="8" t="s">
+      <c r="A43" s="15"/>
+      <c r="B43" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="8"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
     </row>
     <row r="45" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>1</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="7" t="s">
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H45" s="8"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="10">
+      <c r="A46" s="15">
         <v>2</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="7"/>
-      <c r="H46" s="8"/>
+      <c r="F46" s="3"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="10"/>
-      <c r="B47" s="8" t="s">
+      <c r="A47" s="15"/>
+      <c r="B47" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H47" s="8"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
     </row>
     <row r="49" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>1</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="7" t="s">
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H49" s="8"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="10">
+      <c r="A50" s="15">
         <v>2</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F50" s="7"/>
-      <c r="H50" s="8"/>
+      <c r="F50" s="3"/>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="10"/>
-      <c r="B51" s="8" t="s">
+      <c r="A51" s="15"/>
+      <c r="B51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H51" s="8"/>
+      <c r="H51" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -2870,11 +2870,10 @@
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="G26:G27"/>
@@ -2882,20 +2881,21 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>

--- a/docs/03_test/従業員更新のテストケース.xlsx
+++ b/docs/03_test/従業員更新のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4D36B7-2C45-4BDD-9F0D-1ED2FB245910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9498F9EE-9084-4CDF-8E0E-720E84BD0FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D9AB3BAF-20C1-4D8C-BC05-5EA19822F61D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="57">
   <si>
     <t>テストケース① 正常系を用いた一通りの流れのチェック</t>
     <rPh sb="8" eb="11">
@@ -91,95 +91,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員更新単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>スザキ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>チホコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面上部の従業員一覧、またはホーム画面の従業員一覧ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="20" eb="25">
-      <t>ジュウギョウインイチラン</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員一覧画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員ID：1の更新ボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員更新の入力画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ニュウリョクガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>名前を「高橋太郎」に変更して完了ボタンを押す</t>
     <rPh sb="0" eb="2">
       <t>ナマエ</t>
@@ -231,41 +142,6 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員一覧に戻るボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員一覧に遷移し、名前が変更になったことを確認する。</t>
-    <rPh sb="0" eb="5">
-      <t>ジュウギョウインイチラン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -695,41 +571,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員一覧から従業員ID 1：田中太郎の更新ボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>タナカタロウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員更新(入力)画面に遷移する</t>
-    <rPh sb="3" eb="5">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>変更なし</t>
     <rPh sb="0" eb="2">
       <t>ヘンコウ</t>
@@ -741,6 +582,145 @@
   </si>
   <si>
     <t>090-0000-0002</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員更新単体UIテスト 須崎千穂子</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スザキ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>チホコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の社員一覧、またはホーム画面の社員一覧ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧画面に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員ID：1の更新ボタンを押す</t>
+    <rPh sb="7" eb="9">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員更新の入力画面に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ニュウリョクガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧に戻るボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧に遷移し、名前が変更になったことを確認する。</t>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧から社員ID 1：田中太郎の更新ボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>タナカタロウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員更新(入力)画面に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -835,7 +815,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -860,14 +840,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -875,14 +858,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -913,16 +896,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>19830</xdr:colOff>
+      <xdr:colOff>181508</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>1570182</xdr:rowOff>
+      <xdr:rowOff>1158875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB488BD5-DDD4-BE4F-C86A-C7A23E296373}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39F2E1D6-790E-8924-3661-D0E68D589DC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -938,8 +921,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6511636" y="2863273"/>
-          <a:ext cx="2582921" cy="1570182"/>
+          <a:off x="9985375" y="3444875"/>
+          <a:ext cx="3388258" cy="1158875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -953,20 +936,20 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2522017</xdr:colOff>
+      <xdr:colOff>3127375</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1639455</xdr:rowOff>
+      <xdr:rowOff>1338322</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAC43295-2E67-4FF8-E8E7-F64B241CBD2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C724FB50-380D-637E-5CAC-E0F405242B91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -982,8 +965,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6511636" y="4641274"/>
-          <a:ext cx="2522017" cy="1639454"/>
+          <a:off x="9985375" y="5222875"/>
+          <a:ext cx="3127375" cy="1338322"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -996,21 +979,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2542903</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1524001</xdr:rowOff>
+      <xdr:colOff>3190875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1054971</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA663062-43C1-B49D-F37D-EBD7767FD346}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC3B2C90-4095-B56A-79C0-A00A9299E3D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1026,8 +1009,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6511636" y="8024092"/>
-          <a:ext cx="2542903" cy="1524000"/>
+          <a:off x="9985375" y="7127875"/>
+          <a:ext cx="3190875" cy="1054971"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1039,22 +1022,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2126703</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1304637</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>108935</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1285874</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="11" name="図 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4982129E-AE8D-9E09-FCD7-6C1AD67BF89E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F2B2B81-80A2-688D-AA90-54BCE83D80D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1070,8 +1053,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6511637" y="9882910"/>
-          <a:ext cx="2126702" cy="1304636"/>
+          <a:off x="9985375" y="8620124"/>
+          <a:ext cx="3315685" cy="1285875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1084,21 +1067,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1951183</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1255909</xdr:rowOff>
+      <xdr:colOff>3111501</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1094180</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="12" name="図 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FB7258D-2B87-B0FC-46BF-343061975223}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50181EF-73A4-7C7C-ABD5-D84E18E6EFBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1114,8 +1097,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940637" y="12192001"/>
-          <a:ext cx="1951182" cy="1255908"/>
+          <a:off x="9985376" y="10477500"/>
+          <a:ext cx="3111500" cy="1094180"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1127,330 +1110,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
+      <xdr:colOff>3016251</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1276791</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
+        <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F34EDA5-2F0B-4AA7-ADAD-3BCF6E7897BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="15124545"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="図 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F4AB27D-A735-441B-9DAD-E193CE261D15}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="18288000"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64D42B86-58C7-4823-9A88-278F7D38F79C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="21682364"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C343F57-1921-4D82-9049-D4397449AFA5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="24384000"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="図 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8A6BBCE-0EFF-466C-8239-8D43315868CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="27085636"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="図 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F39C0706-CD1D-416A-8B1B-0F4CDF0A40B3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="29787273"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1951182</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>1255908</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED76EC51-A8ED-4022-8159-2E7A16DAF7F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9940636" y="32488909"/>
-          <a:ext cx="1951182" cy="1255908"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1981280</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="図 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B46E63-2A86-42BA-AC03-840687BCB314}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{292A0955-6263-9147-4335-1D9B92890693}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1466,8 +1141,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="13519727"/>
-          <a:ext cx="1981280" cy="1443182"/>
+          <a:off x="9985376" y="12080876"/>
+          <a:ext cx="3016250" cy="1276790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1479,22 +1154,330 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2546625</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1108363</xdr:rowOff>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="図 33">
+        <xdr:cNvPr id="14" name="図 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71F4175F-71D0-A8D5-F584-D2516A278D62}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{130982AD-F247-4FE4-90C3-ECD9DCA9F3DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="14081125"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5256BC7E-2E0F-4D9C-855D-B211ED84DF84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="17002125"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B46CF2B-25F3-423B-83BE-971CEA3E62A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="20145375"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{466D22E6-793A-40DE-ABC4-337FD5891F93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="23383875"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA88B5D2-7407-4BA2-9560-B7D559929D38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="26860500"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51BF0AAC-39BF-449E-A6B1-2DBB6614E280}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="30543500"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>1276790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE53C086-EA08-48C7-BE0A-4C32D06381D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9985375" y="33829625"/>
+          <a:ext cx="3016250" cy="1276790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2778125</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>601845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69F4ECDA-DE84-12D1-FCFE-346DF7E29716}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1510,8 +1493,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940637" y="16452273"/>
-          <a:ext cx="2546624" cy="1339272"/>
+          <a:off x="9985375" y="13414375"/>
+          <a:ext cx="2778125" cy="1363845"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,21 +1507,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1916546</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>1324419</xdr:rowOff>
+      <xdr:colOff>3127375</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>762165</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="図 34">
+        <xdr:cNvPr id="22" name="図 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACC93EEC-A8E1-1DA1-E4CA-D67FBF910B7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DEB0BC5-F5C1-6C5B-29AB-DC79D8871C27}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1554,8 +1537,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="19384818"/>
-          <a:ext cx="1916546" cy="1555328"/>
+          <a:off x="9985375" y="16494125"/>
+          <a:ext cx="3127375" cy="984415"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1568,21 +1551,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>37280</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>1246909</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3159125</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1176825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="図 35">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D10EBB3D-1984-F33C-0855-F307025271C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA44746-1939-F911-9801-1F1773ADA9B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1598,8 +1581,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="22548273"/>
-          <a:ext cx="2600371" cy="1581727"/>
+          <a:off x="9985375" y="19415125"/>
+          <a:ext cx="3159125" cy="1399075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1612,21 +1595,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2413000</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>1095470</xdr:rowOff>
+      <xdr:colOff>3132143</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1016000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="図 36">
+        <xdr:cNvPr id="32" name="図 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F23AFC6D-8DAA-6667-0C5C-40643E942AE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E14E444-8A2A-8FCA-5C07-031E8C5FE8D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1642,8 +1625,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="25792545"/>
-          <a:ext cx="2413000" cy="1661198"/>
+          <a:off x="9985375" y="22558375"/>
+          <a:ext cx="3132143" cy="1349375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1656,21 +1639,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2439457</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>889000</xdr:rowOff>
+      <xdr:colOff>3095625</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>853691</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="図 37">
+        <xdr:cNvPr id="40" name="図 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{875F0401-4782-AB98-9550-D272643E25FA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{302BF024-2846-E400-E29F-68B23374E5A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1686,8 +1669,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="29267727"/>
-          <a:ext cx="2439457" cy="1547091"/>
+          <a:off x="9985375" y="25796875"/>
+          <a:ext cx="3095625" cy="1425191"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1700,21 +1683,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2402035</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>1039091</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57010</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>889000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="図 38">
+        <xdr:cNvPr id="41" name="図 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1400211-0192-E55F-8582-C984147A3343}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B61837BA-294C-B3B1-C540-6229CBE5C79E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1730,8 +1713,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9940636" y="32962273"/>
-          <a:ext cx="2402035" cy="1524000"/>
+          <a:off x="9985375" y="29273500"/>
+          <a:ext cx="3263760" cy="1539875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1744,21 +1727,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2525059</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1185056</xdr:rowOff>
+      <xdr:colOff>3190875</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>867901</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="42" name="図 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8827CF20-9A89-6414-055B-EE6F87026FBB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3275BBE3-2A82-46C3-828F-CFFFCBFB9380}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1774,8 +1757,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9943353" y="7239000"/>
-          <a:ext cx="2525059" cy="1185056"/>
+          <a:off x="9985375" y="32956501"/>
+          <a:ext cx="3190875" cy="1344150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1793,16 +1776,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>2159000</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>133119</xdr:rowOff>
+      <xdr:colOff>2714625</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>995244</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="43" name="図 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6967BE5F-3DCA-E7B8-1232-C88DFA51F3E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A604AEC-7481-4F2C-49C8-5EB4C7E3831B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1818,8 +1801,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9985375" y="35163126"/>
-          <a:ext cx="2159000" cy="1688868"/>
+          <a:off x="9985375" y="36242626"/>
+          <a:ext cx="2714625" cy="1423868"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2128,104 +2111,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766FF2FA-BE58-468F-893B-00485C9954A3}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="24.9140625" customWidth="1"/>
     <col min="4" max="4" width="15.9140625" customWidth="1"/>
     <col min="6" max="6" width="30.1640625" customWidth="1"/>
     <col min="7" max="7" width="33.6640625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="33.6640625" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="41.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="41.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:8" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:9" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="2" t="s">
         <v>3</v>
       </c>
@@ -2233,643 +2219,668 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="140" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" ht="140" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1">
         <v>1</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+      <c r="B15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="3" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" ht="149.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" ht="149.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="B16" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
       <c r="G16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="117" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="117" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="B17" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="146" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>4</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="B18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
       <c r="G18" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="109" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="B19" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1">
         <v>1</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
+      <c r="B21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="15">
+    <row r="22" spans="1:9" ht="59.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="10">
         <v>2</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="10" t="s">
-        <v>31</v>
+      <c r="G22" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="15"/>
+    <row r="23" spans="1:9" ht="59.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="10"/>
       <c r="B23" s="4"/>
       <c r="C23" s="6"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="G23" s="9"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-    </row>
-    <row r="25" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1">
         <v>1</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
+      <c r="B25" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="15">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="10">
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="10"/>
+      <c r="B27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="C27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" ht="90" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="15"/>
-      <c r="B27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1">
         <v>1</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+      <c r="B29" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
       <c r="G29" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="15">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="10">
         <v>2</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" ht="108" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="15"/>
+    <row r="31" spans="1:9" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="10"/>
       <c r="B31" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G31" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="G31" s="11"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-    </row>
-    <row r="33" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1">
         <v>1</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
+      <c r="B33" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
       <c r="G33" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="15">
+    <row r="34" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="10">
         <v>2</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="15"/>
+    <row r="35" spans="1:9" ht="106" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="10"/>
       <c r="B35" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-    </row>
-    <row r="37" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1">
         <v>1</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
+      <c r="B37" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="15">
+    <row r="38" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="10">
         <v>2</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F38" s="3"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="15"/>
+    <row r="39" spans="1:9" ht="106" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="10"/>
       <c r="B39" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-    </row>
-    <row r="41" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1">
         <v>1</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
+      <c r="B41" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
       <c r="G41" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" ht="51.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="15">
+    <row r="42" spans="1:9" ht="51.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="10">
         <v>2</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F42" s="3"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" ht="116.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="15"/>
+    <row r="43" spans="1:9" ht="116.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="10"/>
       <c r="B43" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-    </row>
-    <row r="45" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1">
         <v>1</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
+      <c r="B45" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
       <c r="G45" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="15">
+    <row r="46" spans="1:9" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="10">
         <v>2</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F46" s="3"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="15"/>
+    <row r="47" spans="1:9" ht="98.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="10"/>
       <c r="B47" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="16" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="49" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1">
         <v>1</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
+      <c r="B49" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
       <c r="G49" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="33.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="15">
+      <c r="A50" s="10">
         <v>2</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F50" s="3"/>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="15"/>
+      <c r="A51" s="10"/>
       <c r="B51" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H51" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="A24:H24"/>
@@ -2886,16 +2897,15 @@
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="A46:A47"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -2910,6 +2920,15 @@
     <hyperlink ref="A11" location="ブラックボックステスト!A53" display="⑨同じメールアドレスかつ同じ電話番号が登録されていた場合のエラーチェック" xr:uid="{2285A832-F6FA-4708-8613-CA1F798C5E32}"/>
     <hyperlink ref="C27" r:id="rId1" display="test@csharp.com" xr:uid="{250BB76A-A1E8-462D-961A-98F247851D13}"/>
     <hyperlink ref="C31" r:id="rId2" display="test@csharp.com" xr:uid="{2382E460-357E-41CF-BE23-E43CD0CE1FE3}"/>
+    <hyperlink ref="I13" location="Sheet1!A2" display="目次に戻る" xr:uid="{4D4B4D11-1012-4AF8-A632-E6BC4F413859}"/>
+    <hyperlink ref="I20" location="Sheet1!A2" display="目次に戻る" xr:uid="{57087049-48B7-4F03-AABE-B9038BCD4390}"/>
+    <hyperlink ref="I24" location="Sheet1!A2" display="目次に戻る" xr:uid="{8AB00691-56EB-4C57-B63A-0A983F924155}"/>
+    <hyperlink ref="I28" location="Sheet1!A2" display="目次に戻る" xr:uid="{1F7D18A3-FA58-4F61-AB04-60D1B7C92632}"/>
+    <hyperlink ref="I32" location="Sheet1!A2" display="目次に戻る" xr:uid="{2DEC8318-34E1-4D67-8C5B-13045FE1C28E}"/>
+    <hyperlink ref="I36" location="Sheet1!A2" display="目次に戻る" xr:uid="{B8FDC0D1-DDD3-41A5-BB94-ED547514E825}"/>
+    <hyperlink ref="I40" location="Sheet1!A2" display="目次に戻る" xr:uid="{634B7D3C-399C-4DB5-B498-49DBB8AC4583}"/>
+    <hyperlink ref="I44" location="Sheet1!A2" display="目次に戻る" xr:uid="{95657BFA-7884-4768-9FDA-DF144F764842}"/>
+    <hyperlink ref="I48" location="Sheet1!A2" display="目次に戻る" xr:uid="{4BB21E05-96F3-4117-BC62-4E6407C1A075}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
